--- a/Testes/reescala/Teste populacao e gerações/Teste7/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste7/3_melhor_escala.xlsx
@@ -1072,8 +1072,8 @@
       <c r="P5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>1</v>
@@ -1081,14 +1081,14 @@
       <c r="S5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>0</v>
+      <c r="T5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>0</v>
@@ -1183,8 +1183,8 @@
       <c r="P6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
+      <c r="Q6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>1</v>
@@ -1294,8 +1294,8 @@
       <c r="P7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
+      <c r="Q7" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>1</v>
@@ -1738,8 +1738,8 @@
       <c r="P11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="4" t="n">
-        <v>1</v>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>1</v>
@@ -1747,11 +1747,11 @@
       <c r="S11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0</v>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V11" s="5" t="n">
         <v>0</v>
@@ -3625,8 +3625,8 @@
       <c r="P28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" s="4" t="n">
-        <v>1</v>
+      <c r="Q28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R28" s="4" t="n">
         <v>1</v>
@@ -4561,11 +4561,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -5068,8 +5068,8 @@
       <c r="P41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" s="5" t="n">
-        <v>0</v>
+      <c r="Q41" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0</v>
@@ -5401,8 +5401,8 @@
       <c r="P44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="4" t="n">
-        <v>1</v>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>1</v>
@@ -5521,11 +5521,11 @@
       <c r="S45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" s="5" t="n">
-        <v>0</v>
+      <c r="T45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V45" s="5" t="n">
         <v>0</v>
@@ -5857,8 +5857,8 @@
       <c r="T48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="4" t="n">
-        <v>1</v>
+      <c r="U48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="V48" s="5" t="n">
         <v>0</v>
@@ -5896,8 +5896,8 @@
       <c r="AG48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH48" s="4" t="n">
-        <v>1</v>
+      <c r="AH48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI48" s="5" t="n">
         <v>0</v>
@@ -5956,8 +5956,8 @@
       <c r="P49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="5" t="n">
-        <v>0</v>
+      <c r="Q49" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R49" s="4" t="n">
         <v>1</v>
